--- a/data/trans_bre/P59A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 0,12</t>
+          <t>-6,69; 0,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; -0,41</t>
+          <t>-9,08; -0,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,73</t>
+          <t>-7,92; 0,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -0,02</t>
+          <t>-9,72; 0,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,58; 4,66</t>
+          <t>-64,48; 4,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,99; -0,88</t>
+          <t>-63,21; -5,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 13,17</t>
+          <t>-64,18; 18,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,85; 5,95</t>
+          <t>-68,33; 9,47</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 1,16</t>
+          <t>-6,1; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,45</t>
+          <t>-2,37; 5,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,51</t>
+          <t>-5,72; 1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,04</t>
+          <t>-6,87; 1,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 8,74</t>
+          <t>-38,08; 8,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 42,27</t>
+          <t>-13,68; 39,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 9,57</t>
+          <t>-27,32; 10,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 6,72</t>
+          <t>-37,77; 8,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 6,2</t>
+          <t>-8,94; 5,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 11,18</t>
+          <t>-6,58; 10,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 2,82</t>
+          <t>-11,09; 3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,95</t>
+          <t>-5,48; 7,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 41,43</t>
+          <t>-39,56; 38,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 78,26</t>
+          <t>-28,57; 69,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 16,29</t>
+          <t>-44,4; 18,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 54,36</t>
+          <t>-23,96; 52,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,97</t>
+          <t>-6,08; -0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,03</t>
+          <t>-3,71; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -0,7</t>
+          <t>-6,16; -0,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,09</t>
+          <t>-5,6; 0,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -7,94</t>
+          <t>-40,28; -6,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 15,28</t>
+          <t>-22,54; 13,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -3,97</t>
+          <t>-32,47; -4,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 0,87</t>
+          <t>-32,09; 0,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P59A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-4,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-44,03%</t>
+          <t>-45,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,15</t>
+          <t>-6,92; 0,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -0,62</t>
+          <t>-9,07; -0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 0,91</t>
+          <t>-7,95; 0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 0,31</t>
+          <t>-10,13; -0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 4,97</t>
+          <t>-67,56; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,21; -5,5</t>
+          <t>-62,61; -4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,18; 18,04</t>
+          <t>-64,14; 10,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 9,47</t>
+          <t>-71,07; 3,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,37%</t>
+          <t>-11,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,25</t>
+          <t>-6,04; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,42</t>
+          <t>-2,21; 5,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 1,68</t>
+          <t>-5,9; 1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,22</t>
+          <t>-5,56; 1,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 8,83</t>
+          <t>-36,84; 11,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 39,06</t>
+          <t>-12,85; 40,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 10,26</t>
+          <t>-27,94; 7,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 8,13</t>
+          <t>-29,08; 10,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 5,63</t>
+          <t>-9,58; 5,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 10,83</t>
+          <t>-6,12; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 3,14</t>
+          <t>-11,15; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,78</t>
+          <t>-5,72; 7,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 38,78</t>
+          <t>-42,44; 39,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 69,34</t>
+          <t>-27,11; 76,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 18,9</t>
+          <t>-42,54; 21,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 52,43</t>
+          <t>-24,83; 49,72</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,62%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,73</t>
+          <t>-6,01; -0,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,74</t>
+          <t>-3,98; 1,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -0,67</t>
+          <t>-5,85; -0,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,01</t>
+          <t>-5,5; 0,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -6,54</t>
+          <t>-39,84; -6,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 13,35</t>
+          <t>-23,89; 14,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -4,63</t>
+          <t>-31,31; -4,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 0,2</t>
+          <t>-30,18; 1,0</t>
         </is>
       </c>
     </row>
